--- a/Extras/sprints.xlsx
+++ b/Extras/sprints.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aspa Theodorou\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveplymouthac-my.sharepoint.com/personal/aspasia_theodorou_students_plymouth_ac_uk/Documents/Desktop/COMP1004-Aspa-Theodorou/Extras/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BD5705-25BD-4279-AC0B-06603BF5B21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{17BD5705-25BD-4279-AC0B-06603BF5B21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BDF9179-B667-47C3-B457-57B7CD43845B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Task Tracker" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Task Tracker'!$A$1:$E$56</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="69">
   <si>
     <t>Task</t>
   </si>
@@ -215,9 +218,6 @@
   </si>
   <si>
     <t>Create poster</t>
-  </si>
-  <si>
-    <t>Not Started</t>
   </si>
   <si>
     <t>Write report</t>
@@ -237,7 +237,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -387,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -399,61 +399,67 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -830,811 +836,816 @@
       <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5">
-        <v>46302</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="D2" s="20">
+        <v>45937</v>
+      </c>
+      <c r="E2" s="20">
         <v>46142</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="39.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="9">
+      <c r="C3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="21">
         <v>45937</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="21">
         <v>45951</v>
       </c>
     </row>
     <row r="4" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="13">
+      <c r="B4" s="9"/>
+      <c r="C4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="22">
         <v>45937</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="22">
         <v>45951</v>
       </c>
     </row>
     <row r="5" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="13">
+      <c r="B5" s="9"/>
+      <c r="C5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="22">
         <v>45937</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="22">
         <v>45951</v>
       </c>
     </row>
     <row r="6" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="13">
+      <c r="B6" s="9"/>
+      <c r="C6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="22">
         <v>45937</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="22">
         <v>45951</v>
       </c>
     </row>
     <row r="7" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="13">
+      <c r="B7" s="9"/>
+      <c r="C7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="22">
         <v>45937</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="22">
         <v>45951</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="39.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="9">
+      <c r="C8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="21">
         <v>45952</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="21">
         <v>45965</v>
       </c>
     </row>
     <row r="9" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="B9" s="9"/>
+      <c r="C9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="23">
         <v>45952</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="23">
         <v>45965</v>
       </c>
     </row>
     <row r="10" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="15">
+      <c r="B10" s="9"/>
+      <c r="C10" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="23">
         <v>45952</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="23">
         <v>45965</v>
       </c>
     </row>
     <row r="11" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="B11" s="9"/>
+      <c r="C11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="23">
         <v>45952</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="23">
         <v>45965</v>
       </c>
     </row>
     <row r="12" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="15">
+      <c r="B12" s="9"/>
+      <c r="C12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="23">
         <v>45952</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="23">
         <v>45965</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="39.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="9">
+      <c r="C13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="21">
         <v>45966</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="24">
         <v>45980</v>
       </c>
     </row>
     <row r="14" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="15">
+      <c r="B14" s="12"/>
+      <c r="C14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="23">
         <v>45966</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="22">
         <v>45980</v>
       </c>
     </row>
     <row r="15" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="B15" s="12"/>
+      <c r="C15" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="23">
         <v>45966</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="22">
         <v>45980</v>
       </c>
     </row>
     <row r="16" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="B16" s="12"/>
+      <c r="C16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="23">
         <v>45966</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="22">
         <v>45980</v>
       </c>
     </row>
     <row r="17" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="15">
+      <c r="B17" s="12"/>
+      <c r="C17" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="23">
         <v>45966</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="22">
         <v>45980</v>
       </c>
     </row>
     <row r="18" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="15">
+      <c r="B18" s="12"/>
+      <c r="C18" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="23">
         <v>45966</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="22">
         <v>45980</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="26.4" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:5" ht="39.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="9">
+      <c r="C19" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="21">
         <v>45981</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="24">
         <v>46002</v>
       </c>
     </row>
     <row r="20" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="B20" s="9"/>
+      <c r="C20" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="23">
         <v>45981</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="22">
         <v>46002</v>
       </c>
     </row>
     <row r="21" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="15">
+      <c r="B21" s="9"/>
+      <c r="C21" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="23">
         <v>45981</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="22">
         <v>46002</v>
       </c>
     </row>
     <row r="22" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="B22" s="9"/>
+      <c r="C22" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="23">
         <v>45981</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="22">
         <v>46002</v>
       </c>
     </row>
     <row r="23" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="B23" s="9"/>
+      <c r="C23" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="23">
         <v>45981</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="22">
         <v>46002</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="39.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="16">
+      <c r="C24" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="24">
         <v>46003</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="24">
         <v>46031</v>
       </c>
     </row>
     <row r="25" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="13">
+      <c r="B25" s="12"/>
+      <c r="C25" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="22">
         <v>46003</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="22">
         <v>46010</v>
       </c>
     </row>
     <row r="26" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="13">
+      <c r="B26" s="12"/>
+      <c r="C26" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="22">
         <v>46003</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="22">
         <v>46010</v>
       </c>
     </row>
     <row r="27" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="B27" s="12"/>
+      <c r="C27" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="23">
         <v>46011</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="22">
         <v>46025</v>
       </c>
     </row>
     <row r="28" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="13">
+      <c r="B28" s="12"/>
+      <c r="C28" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="22">
         <v>46026</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="22">
         <v>46031</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="39.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="16">
+      <c r="C29" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="24">
         <v>46032</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="24">
         <v>46053</v>
       </c>
     </row>
     <row r="30" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="13">
+      <c r="B30" s="12"/>
+      <c r="C30" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="22">
         <v>46032</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="22">
         <v>46053</v>
       </c>
     </row>
     <row r="31" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="13">
+      <c r="B31" s="12"/>
+      <c r="C31" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="22">
         <v>46032</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="22">
         <v>46053</v>
       </c>
     </row>
     <row r="32" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="13">
+      <c r="B32" s="12"/>
+      <c r="C32" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="22">
         <v>46032</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="22">
         <v>46053</v>
       </c>
     </row>
     <row r="33" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="13">
+      <c r="B33" s="12"/>
+      <c r="C33" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="22">
         <v>46032</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="22">
         <v>46053</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="39.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="16">
+      <c r="C34" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="24">
         <v>46054</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="24">
         <v>46068</v>
       </c>
     </row>
     <row r="35" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="13">
+      <c r="B35" s="12"/>
+      <c r="C35" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="22">
         <v>46054</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="22">
         <v>46068</v>
       </c>
     </row>
     <row r="36" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="13">
+      <c r="B36" s="12"/>
+      <c r="C36" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="22">
         <v>46054</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="22">
         <v>46068</v>
       </c>
     </row>
     <row r="37" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="13">
+      <c r="B37" s="12"/>
+      <c r="C37" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="22">
         <v>46054</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="22">
         <v>46068</v>
       </c>
     </row>
     <row r="38" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="13">
+      <c r="B38" s="12"/>
+      <c r="C38" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="22">
         <v>46054</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="22">
         <v>46068</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="39.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="16">
+      <c r="C39" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="24">
         <v>46069</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="24">
         <v>46083</v>
       </c>
     </row>
     <row r="40" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="13">
+      <c r="B40" s="9"/>
+      <c r="C40" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="22">
         <v>46069</v>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="22">
         <v>46083</v>
       </c>
     </row>
     <row r="41" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="13">
+      <c r="B41" s="9"/>
+      <c r="C41" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="22">
         <v>46069</v>
       </c>
-      <c r="E41" s="13">
+      <c r="E41" s="22">
         <v>46083</v>
       </c>
     </row>
     <row r="42" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="13">
+      <c r="B42" s="9"/>
+      <c r="C42" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="22">
         <v>46069</v>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="22">
         <v>46083</v>
       </c>
     </row>
     <row r="43" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="13">
+      <c r="B43" s="9"/>
+      <c r="C43" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="22">
         <v>46069</v>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="22">
         <v>46083</v>
       </c>
     </row>
     <row r="44" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" s="13">
+      <c r="B44" s="9"/>
+      <c r="C44" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="22">
         <v>46069</v>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="22">
         <v>46083</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="39.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="19" t="s">
+      <c r="B45" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="16">
+      <c r="C45" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="24">
         <v>46084</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="24">
         <v>46142</v>
       </c>
     </row>
     <row r="46" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" s="13">
+      <c r="B46" s="12"/>
+      <c r="C46" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="22">
         <v>46084</v>
       </c>
-      <c r="E46" s="13">
+      <c r="E46" s="22">
         <v>46098</v>
       </c>
     </row>
     <row r="47" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B47" s="17"/>
-      <c r="C47" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="13">
+      <c r="B47" s="12"/>
+      <c r="C47" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="22">
         <v>46084</v>
       </c>
-      <c r="E47" s="13">
+      <c r="E47" s="22">
         <v>46098</v>
       </c>
     </row>
     <row r="48" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="13">
+      <c r="B48" s="12"/>
+      <c r="C48" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="22">
         <v>46084</v>
       </c>
-      <c r="E48" s="13">
+      <c r="E48" s="22">
         <v>46098</v>
       </c>
     </row>
     <row r="49" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B49" s="17"/>
-      <c r="C49" s="12" t="s">
+      <c r="B49" s="12"/>
+      <c r="C49" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="22">
+        <v>46099</v>
+      </c>
+      <c r="E49" s="22">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A50" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D49" s="13">
+      <c r="B50" s="12"/>
+      <c r="C50" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="22">
         <v>46099</v>
       </c>
-      <c r="E49" s="13">
+      <c r="E50" s="22">
         <v>46110</v>
       </c>
     </row>
-    <row r="50" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A50" s="10" t="s">
+    <row r="51" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A51" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="17"/>
-      <c r="C50" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" s="13">
+      <c r="B51" s="9"/>
+      <c r="C51" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="22">
         <v>46099</v>
       </c>
-      <c r="E50" s="13">
+      <c r="E51" s="22">
         <v>46110</v>
       </c>
     </row>
-    <row r="51" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A51" s="20" t="s">
+    <row r="52" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A52" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D51" s="13">
-        <v>46099</v>
-      </c>
-      <c r="E51" s="13">
-        <v>46110</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A52" s="20" t="s">
+      <c r="B52" s="9"/>
+      <c r="C52" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="22">
+        <v>46111</v>
+      </c>
+      <c r="E52" s="22">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A53" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B52" s="11"/>
-      <c r="C52" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D52" s="13">
-        <v>46111</v>
-      </c>
-      <c r="E52" s="13">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A53" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D53" s="13">
+      <c r="B53" s="9"/>
+      <c r="C53" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="22">
         <v>46130</v>
       </c>
-      <c r="E53" s="13">
+      <c r="E53" s="22">
         <v>46142</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="21"/>
-      <c r="B54" s="22"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="23"/>
+      <c r="A54" s="16"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="21"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
+      <c r="A55" s="16"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions gridLines="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="68" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="33" max="4" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>